--- a/Coatings_db.xlsx
+++ b/Coatings_db.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
   <si>
     <t xml:space="preserve">Code </t>
   </si>
@@ -149,33 +149,6 @@
     <t>Offshore oil rigs, subsea structures splash zone</t>
   </si>
   <si>
-    <t>Base layer for automotive painting (Undercoat)</t>
-  </si>
-  <si>
-    <t>TT-C-490 / ISO 9717</t>
-  </si>
-  <si>
-    <t>Zinc Phosphate Conversion Coating</t>
-  </si>
-  <si>
-    <t>Manganese Phosphate Coating</t>
-  </si>
-  <si>
-    <t>ISO 9717</t>
-  </si>
-  <si>
-    <t>Engine camshafts, gears (Break-in wear &amp; anti-galling)</t>
-  </si>
-  <si>
-    <t>Black Oxide Coating (Fe3O4)</t>
-  </si>
-  <si>
-    <t>MIL-DTL-13924</t>
-  </si>
-  <si>
-    <t>Tooling, indoor firearms (Needs oiling, low corrosion)</t>
-  </si>
-  <si>
     <t>Zinc Electroplated (Clear/Blue)</t>
   </si>
   <si>
@@ -183,6 +156,30 @@
   </si>
   <si>
     <t>ISO 2081 / ASTM B117</t>
+  </si>
+  <si>
+    <t>Galvanic_Potential</t>
+  </si>
+  <si>
+    <t>Coating_Type</t>
+  </si>
+  <si>
+    <t>Anodic</t>
+  </si>
+  <si>
+    <t>Cathodic</t>
+  </si>
+  <si>
+    <t>Barrier</t>
+  </si>
+  <si>
+    <t>Epoxy Primer / Paint Layer</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>Top coat barrier for duplex systems</t>
   </si>
 </sst>
 </file>
@@ -500,10 +497,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -514,47 +511,65 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C2">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2">
+        <v>-0.76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>52</v>
+      <c r="D3">
+        <v>-0.74</v>
       </c>
       <c r="E3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -564,14 +579,20 @@
       <c r="C4">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4">
+        <v>-0.68</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -581,14 +602,20 @@
       <c r="C5">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5">
+        <v>-0.7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -598,14 +625,20 @@
       <c r="C6">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6">
+        <v>-0.78</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -615,14 +648,20 @@
       <c r="C7">
         <v>60</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7">
+        <v>-0.72</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -632,14 +671,20 @@
       <c r="C8">
         <v>50</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8">
+        <v>-0.2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
         <v>21</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -649,14 +694,20 @@
       <c r="C9">
         <v>45</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9">
+        <v>-0.15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
         <v>24</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -666,14 +717,20 @@
       <c r="C10">
         <v>20</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10">
+        <v>-0.25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
         <v>27</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -683,14 +740,20 @@
       <c r="C11">
         <v>40</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11">
+        <v>-0.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
         <v>30</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -700,14 +763,20 @@
       <c r="C12">
         <v>70</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12">
+        <v>-0.45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
         <v>33</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -717,14 +786,20 @@
       <c r="C13">
         <v>35</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13">
+        <v>-0.64</v>
+      </c>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" t="s">
         <v>36</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -734,68 +809,40 @@
       <c r="C14">
         <v>65</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14">
+        <v>-0.8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" t="s">
         <v>39</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16">
-        <v>1.5</v>
-      </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" t="s">
-        <v>46</v>
-      </c>
-      <c r="J16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17">
-        <v>0.5</v>
-      </c>
-      <c r="D17" t="s">
         <v>48</v>
       </c>
-      <c r="E17" t="s">
-        <v>49</v>
-      </c>
-      <c r="J17" t="s">
-        <v>34</v>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
